--- a/human_validation/judge/kor/judge_D003_S003_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D003_S003_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,293 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 사람들이 계속 저한테 잘 안 듣는다고 해서 왔어요. 예를 들면 상사나 아내가 저한테 직접 말을 하고 있는데, 1분쯤 지나면 제가 그중 일부만 들었다는 걸 깨달아요. 그러면 다시 말해달라고 해야 하고, 그게 문제가 되고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 누군가 말할 때 생각이 다른 데로 흘러가는 걸 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네, 거의 그런 식이에요. 누가 저한테 직접 말하고 있어요, 상사든 아내든요. 듣고 있다고 생각하는데, 1분 후에 보면 절반 정도밖에 못 들었다는 걸 깨달아요. 그러면 다시 말해달라고 해야 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 그럴 때 생각이 다른 곳으로 흘러가는 건가요, 아니면 그냥 말하는 내용에 집중하기가 힘든 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네, 그보다는 상대방이 하는 말을 제대로 받아들이지 못하는 쪽에 가까운 것 같아요. 저한테 직접 말하고 있는데, 1분 후에 절반밖에 못 들었다는 걸 깨달아요. 그러면 다시 말해달라고 해야 하는데, 그게 저를 곤란하게 만드는 부분이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 다른 사람의 말을 자주 끊거나 상대가 말을 끝내기 전에 불쑥 대답하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네, 그래요. 특히 회의 때 상사가 질문을 끝내기도 전에 대답해 버려요. 어떨 때는 이미 말을 시작해 놓고, 그제서야 상사가 정작 중요한 부분을 말하기도 전이었다는 걸 깨달아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 일상 업무를 정리하거나 시간을 관리하는 데 어려움이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 그건 잘 모르겠어요. 그러니까, 어떻게든 하루를 보내긴 하는데, 그게 정리정돈이 문제인지 시간이 문제인지 자세히 생각해 본 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 결과를 깊이 생각하지 않고 충동적으로 행동하는 경우가 자주 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네, 그래요. 회사에서 제대로 생각도 안 하고 다른 사람 작업에 끼어들어요. 손을 뻗어서 고치거나 어떻게 하라고 말해주거나 하는 식으로요. 상대가 물어볼 때까지 기다리거나 제 차례를 기다리지 않고, 그러다 보면 이미 그 사람 영역을 침범해 버려서 말다툼이 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 자주 안절부절못하거나 가만히 앉아 있기 힘든 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네. 가만히 앉아 있어야 하면, 가슴이랑 다리에 압박감이 쌓이는 것 같은 느낌이 들어요. 마치 지금 당장 뭔가 움직이거나 해야 할 것 같고, 안 그러면 몸이 근질거려서 견딜 수가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 어린 시절에도 지나치게 활동적이거나 안절부절못하는 편이었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네, 그랬어요. 중학교 들어가기 전, 어렸을 때도 선생님들이 계속 제 자리를 옮기곤 했어요, 제가 가만히 못 있어서요. 답을 불쑥 외치거나 다른 애들 일에 끼어들고 그랬어요. 그것 때문에 많이 혼났어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 직장에서 말씀하신 것처럼, 집에서도 지시사항을 따르거나 일을 끝맺는 데 어려움이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 집에서는 그럭저럭 일을 처리하는 것 같아요. 직장에서처럼 명확한 예가 딱히 떠오르지 않아요. 어떤 지시사항을 말씀하시는 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 앉아 있을 때 손이나 발을 자주 꼼지락거리거나 두드리시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네, 항상 그래요. 안전 회의 때든 저녁 식사 때든, 앉아 있으면 다리가 보통 떨리고 있어요. 펜이나 열쇠를 만지작거리고 있고, 사람들이 제가 벤치나 테이블 전체를 흔들고 있다고 말해주는데, 저는 그러고 있는지도 모르고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 기억나는 한 어릴 때부터 주의를 기울이거나 충동적으로 행동하는 데 어려움이 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네, 기억나는 한 거의 그랬어요. 중학교 들어가기 전에도 선생님들이 계속 제 자리를 옮겼어요, 가만히 못 앉아 있어서요. 답을 불쑥 외치거나 다른 애들 일에 끼어들었고, 그것 때문에 많이 혼났어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 직장 외에 집이나 다른 장소에서도 꼼지락거리거나 가만히 앉아 있기 힘든 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네, 직장만 그런 게 아니에요. 집에서도 저녁 식탁에 앉아 있으면 다리가 계속 떨리고 있어요. 펜이나 열쇠가 있으면 그걸 만지작거리고 있고, 사람들이 제가 벤치나 테이블을 흔들고 있다고 말해주는데, 저는 그걸 하고 있는지도 인식 못 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 이런 주의력과 충동성 문제가 상당한 고통을 주거나 대인관계나 직장 생활에 지장을 주었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 네, 확실히요. 직장에서는 이미 공식 경고를 받을 정도로 심해졌고, 이걸 제어하지 못하면 직장을 잃을 수도 있다는 걱정이 돼요. 라인에서 안전 문제를 일으킬 만한 실수를 할까 봐도 걱정되고요.
+집에서도 문제가 생겨요. 아내랑 아이들이, 제가 일이 순조롭게 되도록 돕기는커녕 오히려 루틴을 흐트러뜨려서 답답해해요. 스트레스 받아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>진단명: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)
 인구통계: 성별 남성 / 나이 42 / 직업상태 production worker / 최종학력 고등학교 졸업
@@ -575,351 +853,43 @@
 증상 지속 기간: 2 years and 2 months
 추가 요건: Onset prior to age 12 years
 주호소 증상 코드: S003
-배경 서술: 하킴의 어려움은 아내가 밖에서 일을 시작하면서 두드러지기 시작했다. 가사 분담이 바뀌면서 그는 예전보다 훨씬 적은 구조 속에서 등하교 픽업, 식사 준비, 초과 근무, 생산 현장 업무를 관리해야 했다. 이후 2년 2개월 동안, 오래전부터 있어 왔던 안절부절못하는 성향이 업무상 장애로 악화되었다. 그는 자리를 지켜야 할 때 자리를 이탈했고, 품질 검사를 서두르다 부주의한 실수를 저질렀으며, 안전 회의 중 상사의 말을 끊고, 부탁받기도 전에 동료의 작업에 끼어들었다. 집에서도 같은 패턴이 계획과 가족 루틴을 흐트러뜨렸고, 직장에서는 그의 움직임과 끼어드는 행동이 조립 라인 협업에 영향을 미치면서 공식 경고로 이어졌다. 상사와 노조 대표가 반복되는 안전 및 품질 문제를 문서로 남긴 후, 그는 직원지원 프로그램 의뢰를 통해 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 사람들이 계속 저한테 잘 안 듣는다고 해서 왔어요. 예를 들면 상사나 아내가 저한테 직접 말을 하고 있는데, 1분쯤 지나면 제가 그중 일부만 들었다는 걸 깨달아요. 그러면 다시 말해달라고 해야 하고, 그게 문제가 되고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 누군가 말할 때 생각이 다른 데로 흘러가는 걸 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네, 거의 그런 식이에요. 누가 저한테 직접 말하고 있어요, 상사든 아내든요. 듣고 있다고 생각하는데, 1분 후에 보면 절반 정도밖에 못 들었다는 걸 깨달아요. 그러면 다시 말해달라고 해야 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 그럴 때 생각이 다른 곳으로 흘러가는 건가요, 아니면 그냥 말하는 내용에 집중하기가 힘든 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네, 그보다는 상대방이 하는 말을 제대로 받아들이지 못하는 쪽에 가까운 것 같아요. 저한테 직접 말하고 있는데, 1분 후에 절반밖에 못 들었다는 걸 깨달아요. 그러면 다시 말해달라고 해야 하는데, 그게 저를 곤란하게 만드는 부분이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 다른 사람의 말을 자주 끊거나 상대가 말을 끝내기 전에 불쑥 대답하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네, 그래요. 특히 회의 때 상사가 질문을 끝내기도 전에 대답해 버려요. 어떨 때는 이미 말을 시작해 놓고, 그제서야 상사가 정작 중요한 부분을 말하기도 전이었다는 걸 깨달아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 일상 업무를 정리하거나 시간을 관리하는 데 어려움이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 그건 잘 모르겠어요. 그러니까, 어떻게든 하루를 보내긴 하는데, 그게 정리정돈이 문제인지 시간이 문제인지 자세히 생각해 본 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 결과를 깊이 생각하지 않고 충동적으로 행동하는 경우가 자주 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네, 그래요. 회사에서 제대로 생각도 안 하고 다른 사람 작업에 끼어들어요. 손을 뻗어서 고치거나 어떻게 하라고 말해주거나 하는 식으로요. 상대가 물어볼 때까지 기다리거나 제 차례를 기다리지 않고, 그러다 보면 이미 그 사람 영역을 침범해 버려서 말다툼이 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 자주 안절부절못하거나 가만히 앉아 있기 힘든 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네. 가만히 앉아 있어야 하면, 가슴이랑 다리에 압박감이 쌓이는 것 같은 느낌이 들어요. 마치 지금 당장 뭔가 움직이거나 해야 할 것 같고, 안 그러면 몸이 근질거려서 견딜 수가 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 어린 시절에도 지나치게 활동적이거나 안절부절못하는 편이었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네, 그랬어요. 중학교 들어가기 전, 어렸을 때도 선생님들이 계속 제 자리를 옮기곤 했어요, 제가 가만히 못 있어서요. 답을 불쑥 외치거나 다른 애들 일에 끼어들고 그랬어요. 그것 때문에 많이 혼났어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 직장에서 말씀하신 것처럼, 집에서도 지시사항을 따르거나 일을 끝맺는 데 어려움이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 집에서는 그럭저럭 일을 처리하는 것 같아요. 직장에서처럼 명확한 예가 딱히 떠오르지 않아요. 어떤 지시사항을 말씀하시는 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 앉아 있을 때 손이나 발을 자주 꼼지락거리거나 두드리시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네, 항상 그래요. 안전 회의 때든 저녁 식사 때든, 앉아 있으면 다리가 보통 떨리고 있어요. 펜이나 열쇠를 만지작거리고 있고, 사람들이 제가 벤치나 테이블 전체를 흔들고 있다고 말해주는데, 저는 그러고 있는지도 모르고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 기억나는 한 어릴 때부터 주의를 기울이거나 충동적으로 행동하는 데 어려움이 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네, 기억나는 한 거의 그랬어요. 중학교 들어가기 전에도 선생님들이 계속 제 자리를 옮겼어요, 가만히 못 앉아 있어서요. 답을 불쑥 외치거나 다른 애들 일에 끼어들었고, 그것 때문에 많이 혼났어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 직장 외에 집이나 다른 장소에서도 꼼지락거리거나 가만히 앉아 있기 힘든 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네, 직장만 그런 게 아니에요. 집에서도 저녁 식탁에 앉아 있으면 다리가 계속 떨리고 있어요. 펜이나 열쇠가 있으면 그걸 만지작거리고 있고, 사람들이 제가 벤치나 테이블을 흔들고 있다고 말해주는데, 저는 그걸 하고 있는지도 인식 못 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 이런 주의력과 충동성 문제가 상당한 고통을 주거나 대인관계나 직장 생활에 지장을 주었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 네, 확실히요. 직장에서는 이미 공식 경고를 받을 정도로 심해졌고, 이걸 제어하지 못하면 직장을 잃을 수도 있다는 걱정이 돼요. 라인에서 안전 문제를 일으킬 만한 실수를 할까 봐도 걱정되고요.
-집에서도 문제가 생겨요. 아내랑 아이들이, 제가 일이 순조롭게 되도록 돕기는커녕 오히려 루틴을 흐트러뜨려서 답답해해요. 스트레스 받아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
+배경 서술: 하킴의 어려움은 아내가 밖에서 일을 시작하면서 두드러지기 시작했다. 가사 분담이 바뀌면서 그는 예전보다 훨씬 적은 구조 속에서 등하교 픽업, 식사 준비, 초과 근무, 생산 현장 업무를 관리해야 했다. 이후 2년 2개월 동안, 오래전부터 있어 왔던 안절부절못하는 성향이 업무상 장애로 악화되었다. 그는 자리를 지켜야 할 때 자리를 이탈했고, 품질 검사를 서두르다 부주의한 실수를 저질렀으며, 안전 회의 중 상사의 말을 끊고, 부탁받기도 전에 동료의 작업에 끼어들었다. 집에서도 같은 패턴이 계획과 가족 루틴을 흐트러뜨렸고, 직장에서는 그의 움직임과 끼어드는 행동이 조립 라인 협업에 영향을 미치면서 공식 경고로 이어졌다. 상사와 노조 대표가 반복되는 안전 및 품질 문제를 문서로 남긴 후, 그는 직원지원 프로그램 의뢰를 통해 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S001 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.
+  - S003 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.
+  - S010 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.
+  - S011 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.
+  - S012 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).
+  - S014 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.
+  - S016 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.
+  - S018 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+        </is>
+      </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: inattention (관계=include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.
-  누락: 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.; 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.; 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.; 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.; 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.; 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.; 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).; 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hyperactivity_impulsivity (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
-  확인된 근거: 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.; 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.; 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).; 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.; 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).
-  누락: 조용한 활동 곤란: 여가 활동을 조용히 하지 못하는 경우가 잦다.; 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.; 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.; 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.</t>
+          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 있음
+체크리스트 그룹: inattention (관계=include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.
+체크리스트 그룹: hyperactivity_impulsivity (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
+확인된 근거:
+  - 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.
+  - 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.
+  - 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).
+  - 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.
+  - 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D003_S003_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D003_S003_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -839,6 +839,11 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -885,11 +890,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D003_S003_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D003_S003_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.3333</v>
+        <v>0.1795</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>0.5385</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.3333</v>
+        <v>0.1795</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.4097</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.9167</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
